--- a/SuppXLS/Scen_Par-Example_Cap.xlsx
+++ b/SuppXLS/Scen_Par-Example_Cap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasiu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5CADA6E-6928-486B-B4D7-5BE0321608F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCE7D18-9B42-4A06-ADF0-D6D59551DF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4603,12 +4603,12 @@
     <row r="8" spans="1:14" ht="35.25" customHeight="1" thickBot="1">
       <c r="A8" s="4"/>
       <c r="B8" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="5"/>
       <c r="F8">
         <f>VLOOKUP(B8,E12:F16,2,FALSE)</f>
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>13</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="L9">
         <f>$F$8*L17</f>
-        <v>3.008</v>
+        <v>0.30080000000000001</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>20</v>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="L10">
         <f t="shared" ref="L10:L14" si="0">$F$8*L18</f>
-        <v>3.3140000000000001</v>
+        <v>0.33140000000000003</v>
       </c>
       <c r="M10" s="18" t="str">
         <f>M9</f>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="L11">
         <f t="shared" si="0"/>
-        <v>3.4880000000000004</v>
+        <v>0.34880000000000005</v>
       </c>
       <c r="M11" s="15" t="str">
         <f t="shared" ref="M11:N14" si="1">M10</f>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="L12">
         <f t="shared" si="0"/>
-        <v>3.6619999999999999</v>
+        <v>0.36619999999999997</v>
       </c>
       <c r="M12" s="18" t="str">
         <f t="shared" si="1"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="L13">
         <f t="shared" si="0"/>
-        <v>3.9020000000000006</v>
+        <v>0.39020000000000005</v>
       </c>
       <c r="M13" s="15" t="str">
         <f t="shared" si="1"/>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L14">
         <f t="shared" si="0"/>
-        <v>4.1159999999999997</v>
+        <v>0.41159999999999997</v>
       </c>
       <c r="M14" s="18" t="str">
         <f t="shared" si="1"/>
@@ -5025,6 +5025,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="833e474d-e424-4496-95f1-98e7780be11a"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="96cf5878-74d7-460f-a445-eb4c85d99a58">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008FCB31E966C8774491137362174F34D4" ma:contentTypeVersion="15" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="62805c5ff75ed3eac4b8d2b4851418ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="96cf5878-74d7-460f-a445-eb4c85d99a58" xmlns:ns3="833e474d-e424-4496-95f1-98e7780be11a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ccf88e0e58cdad9665a0e2e567230cdf" ns2:_="" ns3:_="">
     <xsd:import namespace="96cf5878-74d7-460f-a445-eb4c85d99a58"/>
@@ -5259,41 +5279,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="833e474d-e424-4496-95f1-98e7780be11a"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="96cf5878-74d7-460f-a445-eb4c85d99a58">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1C93F2F-89BC-4417-BAF2-D0C21FA38791}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A976D7-35DB-4A8F-8FCE-7F2E5428504C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="96cf5878-74d7-460f-a445-eb4c85d99a58"/>
-    <ds:schemaRef ds:uri="833e474d-e424-4496-95f1-98e7780be11a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5316,9 +5305,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A976D7-35DB-4A8F-8FCE-7F2E5428504C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1C93F2F-89BC-4417-BAF2-D0C21FA38791}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="96cf5878-74d7-460f-a445-eb4c85d99a58"/>
+    <ds:schemaRef ds:uri="833e474d-e424-4496-95f1-98e7780be11a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>